--- a/2022 data/excel_outputs/189_boothwise_data.xlsx
+++ b/2022 data/excel_outputs/189_boothwise_data.xlsx
@@ -14,11 +14,68 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="411">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="456">
   <si>
     <t>AC 189 Booth-wise Data</t>
   </si>
   <si>
+    <t>Unnamed: 1</t>
+  </si>
+  <si>
+    <t>Unnamed: 2</t>
+  </si>
+  <si>
+    <t>Unnamed: 3</t>
+  </si>
+  <si>
+    <t>Unnamed: 4</t>
+  </si>
+  <si>
+    <t>Unnamed: 5</t>
+  </si>
+  <si>
+    <t>Unnamed: 6</t>
+  </si>
+  <si>
+    <t>Unnamed: 7</t>
+  </si>
+  <si>
+    <t>Unnamed: 8</t>
+  </si>
+  <si>
+    <t>Unnamed: 9</t>
+  </si>
+  <si>
+    <t>Unnamed: 10</t>
+  </si>
+  <si>
+    <t>Unnamed: 11</t>
+  </si>
+  <si>
+    <t>Unnamed: 12</t>
+  </si>
+  <si>
+    <t>Unnamed: 13</t>
+  </si>
+  <si>
+    <t>Unnamed: 14</t>
+  </si>
+  <si>
+    <t>Unnamed: 15</t>
+  </si>
+  <si>
+    <t>Unnamed: 16</t>
+  </si>
+  <si>
+    <t>Unnamed: 17</t>
+  </si>
+  <si>
+    <t>Unnamed: 18</t>
+  </si>
+  <si>
+    <t>Unnamed: 19</t>
+  </si>
+  <si>
     <t>BOOTH ID</t>
   </si>
   <si>
@@ -1093,106 +1150,184 @@
     <t>praathmik vidyaaly jaajuupur kkss sN0 1</t>
   </si>
   <si>
-    <t>##0##0 ####0 ####### #### ##01</t>
-  </si>
-  <si>
-    <t>##0 ##0 ####0 ####### #### ##0 2</t>
-  </si>
-  <si>
-    <t>##0 ##0 ####0 ####### #### ##0 3</t>
-  </si>
-  <si>
-    <t>####0 ##0 ############# #### ##0 1</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ####### #### ##0 #</t>
-  </si>
-  <si>
-    <t>####0 ##0 ####### #### ##01</t>
-  </si>
-  <si>
-    <t>####0##0 ####### #### ##0 #</t>
-  </si>
-  <si>
-    <t>####0 ##0 ####### ###0 ####</t>
-  </si>
-  <si>
-    <t>####0 ##0 ###### #### ##01</t>
-  </si>
-  <si>
-    <t>####0##0 ###### #### ##0 #</t>
-  </si>
-  <si>
-    <t>####0 ##0 ####### ######0 1</t>
-  </si>
-  <si>
-    <t>####0 ##0 ####### ######0 2</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ######## ####</t>
-  </si>
-  <si>
-    <t>####0 ##0 ##### #### #### ##01</t>
-  </si>
-  <si>
-    <t>####0##0 ##### #### #### ##0 #</t>
-  </si>
-  <si>
-    <t>####0 ### ##### #### #### ##02</t>
-  </si>
-  <si>
-    <t>####0 ### ##### #### ######## ####</t>
-  </si>
-  <si>
-    <t>####0 ##0 #### #### ##0 1</t>
-  </si>
-  <si>
-    <t>####0 ##0 #### ######0 2</t>
-  </si>
-  <si>
-    <t>####0 ##0 #### ######0 3</t>
-  </si>
-  <si>
-    <t>####0 ##0 ###### #### ##0 1</t>
-  </si>
-  <si>
-    <t>####0 ##0 #### #### ##0 2</t>
-  </si>
-  <si>
-    <t>#### ###### ##0##0####0 ##### ######## #### ##0 #</t>
-  </si>
-  <si>
-    <t>####0##0 ##### #### ##0 #</t>
-  </si>
-  <si>
-    <t>####0##0 ######### #### ##0 #</t>
-  </si>
-  <si>
-    <t>####0##0 ######## #### ##0 #</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ########## #### ##0 #</t>
-  </si>
-  <si>
-    <t>####0##0 ####### dvitiiy #### ##0 #</t>
-  </si>
-  <si>
-    <t>####0##0 ########## #### ##0 #</t>
-  </si>
-  <si>
-    <t>####0##0 ;#######ddh ######## ######## #### ##0 #</t>
-  </si>
-  <si>
-    <t>####0##0 ######## #### #### ##0 #</t>
-  </si>
-  <si>
-    <t>##### ####0##0 ######## #### ##0 #</t>
-  </si>
-  <si>
-    <t>####0##0 shriiraampur ##### #### ##0 #</t>
-  </si>
-  <si>
-    <t>####0##0 shriiraampur ##### #### ##0 2</t>
+    <t>praathmik vidyaaly jaajuupur kkss sN0 1 ROOM NO. 361</t>
+  </si>
+  <si>
+    <t>praathmik vidyaaly jaajuupur kkss sN0 1 ROOM ROOM NO. 362</t>
+  </si>
+  <si>
+    <t>praathmik vidyaaly jaajuupur kkss sN0 1 ROOM ROOM ROOM NO. 363</t>
+  </si>
+  <si>
+    <t>praathmik vidyaaly jaajuupur kkss sN0 1 ROOM ROOM ROOM ROOM NO. 364</t>
+  </si>
+  <si>
+    <t>praathmik vidyaaly jaajuupur kkss sN0 1 ROOM ROOM ROOM ROOM ROOM NO. 365</t>
+  </si>
+  <si>
+    <t>praathmik vidyaaly jaajuupur kkss sN0 1 ROOM ROOM ROOM ROOM ROOM ROOM NO. 366</t>
+  </si>
+  <si>
+    <t>praathmik vidyaaly jaajuupur kkss sN0 1 ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 367</t>
+  </si>
+  <si>
+    <t>praathmik vidyaaly jaajuupur kkss sN0 1 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 368</t>
+  </si>
+  <si>
+    <t>praathmik vidyaaly jaajuupur kkss sN0 1 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 369</t>
+  </si>
+  <si>
+    <t>praathmik vidyaaly jaajuupur kkss sN0 1 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 370</t>
+  </si>
+  <si>
+    <t>praathmik vidyaaly jaajuupur kkss sN0 1 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 371</t>
+  </si>
+  <si>
+    <t>praathmik vidyaaly jaajuupur kkss sN0 1 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 372</t>
+  </si>
+  <si>
+    <t>praathmik vidyaaly jaajuupur kkss sN0 1 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 373</t>
+  </si>
+  <si>
+    <t>praathmik vidyaaly jaajuupur kkss sN0 1 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 374</t>
+  </si>
+  <si>
+    <t>praathmik vidyaaly jaajuupur kkss sN0 1 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 375</t>
+  </si>
+  <si>
+    <t>praathmik vidyaaly jaajuupur kkss sN0 1 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 376</t>
+  </si>
+  <si>
+    <t>praathmik vidyaaly jaajuupur kkss sN0 1 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 377</t>
+  </si>
+  <si>
+    <t>praathmik vidyaaly jaajuupur kkss sN0 1 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 378</t>
+  </si>
+  <si>
+    <t>praathmik vidyaaly jaajuupur kkss sN0 1 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 379</t>
+  </si>
+  <si>
+    <t>praathmik vidyaaly jaajuupur kkss sN0 1 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 380</t>
+  </si>
+  <si>
+    <t>praathmik vidyaaly jaajuupur kkss sN0 1 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 381</t>
+  </si>
+  <si>
+    <t>praathmik vidyaaly jaajuupur kkss sN0 1 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 382</t>
+  </si>
+  <si>
+    <t>praathmik vidyaaly jaajuupur kkss sN0 1 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 383</t>
+  </si>
+  <si>
+    <t>praathmik vidyaaly jaajuupur kkss sN0 1 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 384</t>
+  </si>
+  <si>
+    <t>praathmik vidyaaly jaajuupur kkss sN0 1 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 385</t>
+  </si>
+  <si>
+    <t>praathmik vidyaaly jaajuupur kkss sN0 1 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 386</t>
+  </si>
+  <si>
+    <t>praathmik vidyaaly jaajuupur kkss sN0 1 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 387</t>
+  </si>
+  <si>
+    <t>praathmik vidyaaly jaajuupur kkss sN0 1 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 388</t>
+  </si>
+  <si>
+    <t>praathmik vidyaaly jaajuupur kkss sN0 1 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 389</t>
+  </si>
+  <si>
+    <t>praathmik vidyaaly jaajuupur kkss sN0 1 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 390</t>
+  </si>
+  <si>
+    <t>praathmik vidyaaly jaajuupur kkss sN0 1 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 391</t>
+  </si>
+  <si>
+    <t>praathmik vidyaaly jaajuupur kkss sN0 1 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 392</t>
+  </si>
+  <si>
+    <t>praathmik vidyaaly jaajuupur kkss sN0 1 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 393</t>
+  </si>
+  <si>
+    <t>praathmik vidyaaly jaajuupur kkss sN0 1 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 394</t>
+  </si>
+  <si>
+    <t>praathmik vidyaaly jaajuupur kkss sN0 1 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 395</t>
+  </si>
+  <si>
+    <t>praathmik vidyaaly jaajuupur kkss sN0 1 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 396</t>
+  </si>
+  <si>
+    <t>praathmik vidyaaly jaajuupur kkss sN0 1 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 397</t>
+  </si>
+  <si>
+    <t>praathmik vidyaaly jaajuupur kkss sN0 1 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 398</t>
+  </si>
+  <si>
+    <t>praathmik vidyaaly jaajuupur kkss sN0 1 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 399</t>
+  </si>
+  <si>
+    <t>praathmik vidyaaly jaajuupur kkss sN0 1 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 400</t>
+  </si>
+  <si>
+    <t>praathmik vidyaaly jaajuupur kkss sN0 1 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 401</t>
+  </si>
+  <si>
+    <t>praathmik vidyaaly jaajuupur kkss sN0 1 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 402</t>
+  </si>
+  <si>
+    <t>praathmik vidyaaly jaajuupur kkss sN0 1 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 403</t>
+  </si>
+  <si>
+    <t>praathmik vidyaaly jaajuupur kkss sN0 1 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 404</t>
+  </si>
+  <si>
+    <t>praathmik vidyaaly jaajuupur kkss sN0 1 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 405</t>
+  </si>
+  <si>
+    <t>praathmik vidyaaly jaajuupur kkss sN0 1 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 406</t>
+  </si>
+  <si>
+    <t>praathmik vidyaaly jaajuupur kkss sN0 1 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 407</t>
+  </si>
+  <si>
+    <t>praathmik vidyaaly jaajuupur kkss sN0 1 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 408</t>
+  </si>
+  <si>
+    <t>praathmik vidyaaly jaajuupur kkss sN0 1 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 409</t>
+  </si>
+  <si>
+    <t>praathmik vidyaaly jaajuupur kkss sN0 1 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 410</t>
+  </si>
+  <si>
+    <t>praathmik vidyaaly jaajuupur kkss sN0 1 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 411</t>
+  </si>
+  <si>
+    <t>praathmik vidyaaly jaajuupur kkss sN0 1 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 412</t>
+  </si>
+  <si>
+    <t>praathmik vidyaaly jaajuupur kkss sN0 1 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 413</t>
+  </si>
+  <si>
+    <t>praathmik vidyaaly jaajuupur kkss sN0 1 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 414</t>
+  </si>
+  <si>
+    <t>praathmik vidyaaly jaajuupur kkss sN0 1 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 415</t>
+  </si>
+  <si>
+    <t>praathmik vidyaaly jaajuupur kkss sN0 1 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 416</t>
+  </si>
+  <si>
+    <t>praathmik vidyaaly jaajuupur kkss sN0 1 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 417</t>
+  </si>
+  <si>
+    <t>praathmik vidyaaly jaajuupur kkss sN0 1 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 418</t>
+  </si>
+  <si>
+    <t>praathmik vidyaaly jaajuupur kkss sN0 1 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 419</t>
+  </si>
+  <si>
+    <t>praathmik vidyaaly jaajuupur kkss sN0 1 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 420</t>
   </si>
   <si>
     <t>TOTAL ELECTORS</t>
@@ -1253,8 +1388,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -1270,7 +1413,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1278,12 +1421,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1582,70 +1743,127 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:20">
-      <c r="A1" t="s">
-        <v>0</v>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>393</v>
+        <v>438</v>
       </c>
       <c r="D2" t="s">
-        <v>394</v>
+        <v>439</v>
       </c>
       <c r="E2" t="s">
-        <v>395</v>
+        <v>440</v>
       </c>
       <c r="F2" t="s">
-        <v>396</v>
+        <v>441</v>
       </c>
       <c r="G2" t="s">
-        <v>397</v>
+        <v>442</v>
       </c>
       <c r="H2" t="s">
-        <v>398</v>
+        <v>443</v>
       </c>
       <c r="I2" t="s">
-        <v>399</v>
+        <v>444</v>
       </c>
       <c r="J2" t="s">
-        <v>400</v>
+        <v>445</v>
       </c>
       <c r="K2" t="s">
-        <v>401</v>
+        <v>446</v>
       </c>
       <c r="L2" t="s">
-        <v>402</v>
+        <v>447</v>
       </c>
       <c r="M2" t="s">
-        <v>403</v>
+        <v>448</v>
       </c>
       <c r="N2" t="s">
-        <v>404</v>
+        <v>449</v>
       </c>
       <c r="O2" t="s">
-        <v>405</v>
+        <v>450</v>
       </c>
       <c r="P2" t="s">
-        <v>406</v>
+        <v>451</v>
       </c>
       <c r="Q2" t="s">
-        <v>407</v>
+        <v>452</v>
       </c>
       <c r="R2" t="s">
-        <v>408</v>
+        <v>453</v>
       </c>
       <c r="S2" t="s">
-        <v>409</v>
+        <v>454</v>
       </c>
       <c r="T2" t="s">
-        <v>410</v>
+        <v>455</v>
       </c>
     </row>
     <row r="3" spans="1:20">
@@ -1653,7 +1871,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="C3">
         <v>1162</v>
@@ -1715,7 +1933,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="C4">
         <v>814</v>
@@ -1777,7 +1995,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="C5">
         <v>856</v>
@@ -1839,7 +2057,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="C6">
         <v>1124</v>
@@ -1901,7 +2119,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="C7">
         <v>972</v>
@@ -1963,7 +2181,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="C8">
         <v>954</v>
@@ -2025,7 +2243,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="C9">
         <v>561</v>
@@ -2087,7 +2305,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="C10">
         <v>881</v>
@@ -2149,7 +2367,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="C11">
         <v>803</v>
@@ -2211,7 +2429,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="C12">
         <v>830</v>
@@ -2273,7 +2491,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="C13">
         <v>887</v>
@@ -2335,7 +2553,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="C14">
         <v>725</v>
@@ -2397,7 +2615,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="C15">
         <v>595</v>
@@ -2459,7 +2677,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="C16">
         <v>559</v>
@@ -2521,7 +2739,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="C17">
         <v>1051</v>
@@ -2583,7 +2801,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="C18">
         <v>786</v>
@@ -2645,7 +2863,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="C19">
         <v>578</v>
@@ -2707,7 +2925,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="C20">
         <v>524</v>
@@ -2769,7 +2987,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="C21">
         <v>720</v>
@@ -2831,7 +3049,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="C22">
         <v>682</v>
@@ -2893,7 +3111,7 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="C23">
         <v>648</v>
@@ -2955,7 +3173,7 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="C24">
         <v>720</v>
@@ -3017,7 +3235,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="C25">
         <v>1082</v>
@@ -3079,7 +3297,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="C26">
         <v>643</v>
@@ -3141,7 +3359,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="C27">
         <v>594</v>
@@ -3203,7 +3421,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="C28">
         <v>1193</v>
@@ -3265,7 +3483,7 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="C29">
         <v>974</v>
@@ -3327,7 +3545,7 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="C30">
         <v>896</v>
@@ -3389,7 +3607,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="C31">
         <v>588</v>
@@ -3451,7 +3669,7 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="C32">
         <v>1063</v>
@@ -3513,7 +3731,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="C33">
         <v>735</v>
@@ -3575,7 +3793,7 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="C34">
         <v>827</v>
@@ -3637,7 +3855,7 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="C35">
         <v>796</v>
@@ -3699,7 +3917,7 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="C36">
         <v>1087</v>
@@ -3761,7 +3979,7 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="C37">
         <v>1175</v>
@@ -3823,7 +4041,7 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="C38">
         <v>1127</v>
@@ -3885,7 +4103,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="C39">
         <v>1147</v>
@@ -3947,7 +4165,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>40</v>
+        <v>59</v>
       </c>
       <c r="C40">
         <v>895</v>
@@ -4009,7 +4227,7 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="C41">
         <v>514</v>
@@ -4071,7 +4289,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="C42">
         <v>529</v>
@@ -4133,7 +4351,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="C43">
         <v>695</v>
@@ -4195,7 +4413,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="C44">
         <v>553</v>
@@ -4257,7 +4475,7 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="C45">
         <v>1122</v>
@@ -4319,7 +4537,7 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="C46">
         <v>1124</v>
@@ -4381,7 +4599,7 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="C47">
         <v>941</v>
@@ -4443,7 +4661,7 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="C48">
         <v>714</v>
@@ -4505,7 +4723,7 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>49</v>
+        <v>68</v>
       </c>
       <c r="C49">
         <v>839</v>
@@ -4567,7 +4785,7 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="C50">
         <v>942</v>
@@ -4629,7 +4847,7 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="C51">
         <v>498</v>
@@ -4691,7 +4909,7 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="C52">
         <v>1019</v>
@@ -4753,7 +4971,7 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="C53">
         <v>704</v>
@@ -4815,7 +5033,7 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>54</v>
+        <v>73</v>
       </c>
       <c r="C54">
         <v>705</v>
@@ -4877,7 +5095,7 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>55</v>
+        <v>74</v>
       </c>
       <c r="C55">
         <v>672</v>
@@ -4939,7 +5157,7 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="C56">
         <v>661</v>
@@ -5001,7 +5219,7 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="C57">
         <v>1088</v>
@@ -5063,7 +5281,7 @@
         <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>58</v>
+        <v>77</v>
       </c>
       <c r="C58">
         <v>949</v>
@@ -5125,7 +5343,7 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>59</v>
+        <v>78</v>
       </c>
       <c r="C59">
         <v>592</v>
@@ -5187,7 +5405,7 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="C60">
         <v>589</v>
@@ -5249,7 +5467,7 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="C61">
         <v>767</v>
@@ -5311,7 +5529,7 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>62</v>
+        <v>81</v>
       </c>
       <c r="C62">
         <v>507</v>
@@ -5373,7 +5591,7 @@
         <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="C63">
         <v>1111</v>
@@ -5435,7 +5653,7 @@
         <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="C64">
         <v>648</v>
@@ -5497,7 +5715,7 @@
         <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="C65">
         <v>736</v>
@@ -5559,7 +5777,7 @@
         <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c r="C66">
         <v>677</v>
@@ -5621,7 +5839,7 @@
         <v>65</v>
       </c>
       <c r="B67" t="s">
-        <v>67</v>
+        <v>86</v>
       </c>
       <c r="C67">
         <v>602</v>
@@ -5683,7 +5901,7 @@
         <v>66</v>
       </c>
       <c r="B68" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
       <c r="C68">
         <v>953</v>
@@ -5745,7 +5963,7 @@
         <v>67</v>
       </c>
       <c r="B69" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="C69">
         <v>910</v>
@@ -5807,7 +6025,7 @@
         <v>68</v>
       </c>
       <c r="B70" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="C70">
         <v>1103</v>
@@ -5869,7 +6087,7 @@
         <v>69</v>
       </c>
       <c r="B71" t="s">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="C71">
         <v>1104</v>
@@ -5931,7 +6149,7 @@
         <v>70</v>
       </c>
       <c r="B72" t="s">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="C72">
         <v>610</v>
@@ -5993,7 +6211,7 @@
         <v>71</v>
       </c>
       <c r="B73" t="s">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="C73">
         <v>650</v>
@@ -6055,7 +6273,7 @@
         <v>72</v>
       </c>
       <c r="B74" t="s">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="C74">
         <v>660</v>
@@ -6117,7 +6335,7 @@
         <v>73</v>
       </c>
       <c r="B75" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="C75">
         <v>814</v>
@@ -6179,7 +6397,7 @@
         <v>74</v>
       </c>
       <c r="B76" t="s">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="C76">
         <v>728</v>
@@ -6241,7 +6459,7 @@
         <v>75</v>
       </c>
       <c r="B77" t="s">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="C77">
         <v>809</v>
@@ -6303,7 +6521,7 @@
         <v>76</v>
       </c>
       <c r="B78" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="C78">
         <v>849</v>
@@ -6365,7 +6583,7 @@
         <v>77</v>
       </c>
       <c r="B79" t="s">
-        <v>79</v>
+        <v>98</v>
       </c>
       <c r="C79">
         <v>652</v>
@@ -6427,7 +6645,7 @@
         <v>78</v>
       </c>
       <c r="B80" t="s">
-        <v>80</v>
+        <v>99</v>
       </c>
       <c r="C80">
         <v>1099</v>
@@ -6489,7 +6707,7 @@
         <v>79</v>
       </c>
       <c r="B81" t="s">
-        <v>81</v>
+        <v>100</v>
       </c>
       <c r="C81">
         <v>671</v>
@@ -6551,7 +6769,7 @@
         <v>80</v>
       </c>
       <c r="B82" t="s">
-        <v>82</v>
+        <v>101</v>
       </c>
       <c r="C82">
         <v>521</v>
@@ -6613,7 +6831,7 @@
         <v>81</v>
       </c>
       <c r="B83" t="s">
-        <v>83</v>
+        <v>102</v>
       </c>
       <c r="C83">
         <v>969</v>
@@ -6675,7 +6893,7 @@
         <v>82</v>
       </c>
       <c r="B84" t="s">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="C84">
         <v>1113</v>
@@ -6737,7 +6955,7 @@
         <v>83</v>
       </c>
       <c r="B85" t="s">
-        <v>85</v>
+        <v>104</v>
       </c>
       <c r="C85">
         <v>1034</v>
@@ -6799,7 +7017,7 @@
         <v>84</v>
       </c>
       <c r="B86" t="s">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="C86">
         <v>821</v>
@@ -6861,7 +7079,7 @@
         <v>85</v>
       </c>
       <c r="B87" t="s">
-        <v>87</v>
+        <v>106</v>
       </c>
       <c r="C87">
         <v>1124</v>
@@ -6923,7 +7141,7 @@
         <v>86</v>
       </c>
       <c r="B88" t="s">
-        <v>88</v>
+        <v>107</v>
       </c>
       <c r="C88">
         <v>984</v>
@@ -6985,7 +7203,7 @@
         <v>87</v>
       </c>
       <c r="B89" t="s">
-        <v>89</v>
+        <v>108</v>
       </c>
       <c r="C89">
         <v>555</v>
@@ -7047,7 +7265,7 @@
         <v>88</v>
       </c>
       <c r="B90" t="s">
-        <v>90</v>
+        <v>109</v>
       </c>
       <c r="C90">
         <v>842</v>
@@ -7109,7 +7327,7 @@
         <v>89</v>
       </c>
       <c r="B91" t="s">
-        <v>91</v>
+        <v>110</v>
       </c>
       <c r="C91">
         <v>641</v>
@@ -7171,7 +7389,7 @@
         <v>90</v>
       </c>
       <c r="B92" t="s">
-        <v>92</v>
+        <v>111</v>
       </c>
       <c r="C92">
         <v>1136</v>
@@ -7233,7 +7451,7 @@
         <v>91</v>
       </c>
       <c r="B93" t="s">
-        <v>93</v>
+        <v>112</v>
       </c>
       <c r="C93">
         <v>1167</v>
@@ -7295,7 +7513,7 @@
         <v>92</v>
       </c>
       <c r="B94" t="s">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="C94">
         <v>1027</v>
@@ -7357,7 +7575,7 @@
         <v>93</v>
       </c>
       <c r="B95" t="s">
-        <v>95</v>
+        <v>114</v>
       </c>
       <c r="C95">
         <v>1056</v>
@@ -7419,7 +7637,7 @@
         <v>94</v>
       </c>
       <c r="B96" t="s">
-        <v>96</v>
+        <v>115</v>
       </c>
       <c r="C96">
         <v>649</v>
@@ -7481,7 +7699,7 @@
         <v>95</v>
       </c>
       <c r="B97" t="s">
-        <v>97</v>
+        <v>116</v>
       </c>
       <c r="C97">
         <v>786</v>
@@ -7543,7 +7761,7 @@
         <v>96</v>
       </c>
       <c r="B98" t="s">
-        <v>98</v>
+        <v>117</v>
       </c>
       <c r="C98">
         <v>1184</v>
@@ -7605,7 +7823,7 @@
         <v>97</v>
       </c>
       <c r="B99" t="s">
-        <v>99</v>
+        <v>118</v>
       </c>
       <c r="C99">
         <v>949</v>
@@ -7667,7 +7885,7 @@
         <v>98</v>
       </c>
       <c r="B100" t="s">
-        <v>100</v>
+        <v>119</v>
       </c>
       <c r="C100">
         <v>816</v>
@@ -7729,7 +7947,7 @@
         <v>99</v>
       </c>
       <c r="B101" t="s">
-        <v>101</v>
+        <v>120</v>
       </c>
       <c r="C101">
         <v>991</v>
@@ -7791,7 +8009,7 @@
         <v>100</v>
       </c>
       <c r="B102" t="s">
-        <v>102</v>
+        <v>121</v>
       </c>
       <c r="C102">
         <v>667</v>
@@ -7853,7 +8071,7 @@
         <v>101</v>
       </c>
       <c r="B103" t="s">
-        <v>103</v>
+        <v>122</v>
       </c>
       <c r="C103">
         <v>602</v>
@@ -7915,7 +8133,7 @@
         <v>102</v>
       </c>
       <c r="B104" t="s">
-        <v>104</v>
+        <v>123</v>
       </c>
       <c r="C104">
         <v>983</v>
@@ -7977,7 +8195,7 @@
         <v>103</v>
       </c>
       <c r="B105" t="s">
-        <v>105</v>
+        <v>124</v>
       </c>
       <c r="C105">
         <v>1153</v>
@@ -8039,7 +8257,7 @@
         <v>104</v>
       </c>
       <c r="B106" t="s">
-        <v>106</v>
+        <v>125</v>
       </c>
       <c r="C106">
         <v>859</v>
@@ -8101,7 +8319,7 @@
         <v>105</v>
       </c>
       <c r="B107" t="s">
-        <v>107</v>
+        <v>126</v>
       </c>
       <c r="C107">
         <v>1175</v>
@@ -8163,7 +8381,7 @@
         <v>106</v>
       </c>
       <c r="B108" t="s">
-        <v>108</v>
+        <v>127</v>
       </c>
       <c r="C108">
         <v>813</v>
@@ -8225,7 +8443,7 @@
         <v>107</v>
       </c>
       <c r="B109" t="s">
-        <v>109</v>
+        <v>128</v>
       </c>
       <c r="C109">
         <v>388</v>
@@ -8287,7 +8505,7 @@
         <v>108</v>
       </c>
       <c r="B110" t="s">
-        <v>110</v>
+        <v>129</v>
       </c>
       <c r="C110">
         <v>812</v>
@@ -8349,7 +8567,7 @@
         <v>109</v>
       </c>
       <c r="B111" t="s">
-        <v>111</v>
+        <v>130</v>
       </c>
       <c r="C111">
         <v>637</v>
@@ -8411,7 +8629,7 @@
         <v>110</v>
       </c>
       <c r="B112" t="s">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="C112">
         <v>449</v>
@@ -8473,7 +8691,7 @@
         <v>111</v>
       </c>
       <c r="B113" t="s">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="C113">
         <v>496</v>
@@ -8535,7 +8753,7 @@
         <v>112</v>
       </c>
       <c r="B114" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="C114">
         <v>691</v>
@@ -8597,7 +8815,7 @@
         <v>113</v>
       </c>
       <c r="B115" t="s">
-        <v>115</v>
+        <v>134</v>
       </c>
       <c r="C115">
         <v>724</v>
@@ -8659,7 +8877,7 @@
         <v>114</v>
       </c>
       <c r="B116" t="s">
-        <v>116</v>
+        <v>135</v>
       </c>
       <c r="C116">
         <v>776</v>
@@ -8721,7 +8939,7 @@
         <v>115</v>
       </c>
       <c r="B117" t="s">
-        <v>117</v>
+        <v>136</v>
       </c>
       <c r="C117">
         <v>1115</v>
@@ -8783,7 +9001,7 @@
         <v>116</v>
       </c>
       <c r="B118" t="s">
-        <v>118</v>
+        <v>137</v>
       </c>
       <c r="C118">
         <v>1164</v>
@@ -8845,7 +9063,7 @@
         <v>117</v>
       </c>
       <c r="B119" t="s">
-        <v>119</v>
+        <v>138</v>
       </c>
       <c r="C119">
         <v>563</v>
@@ -8907,7 +9125,7 @@
         <v>118</v>
       </c>
       <c r="B120" t="s">
-        <v>120</v>
+        <v>139</v>
       </c>
       <c r="C120">
         <v>841</v>
@@ -8969,7 +9187,7 @@
         <v>119</v>
       </c>
       <c r="B121" t="s">
-        <v>121</v>
+        <v>140</v>
       </c>
       <c r="C121">
         <v>782</v>
@@ -9031,7 +9249,7 @@
         <v>120</v>
       </c>
       <c r="B122" t="s">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="C122">
         <v>782</v>
@@ -9093,7 +9311,7 @@
         <v>121</v>
       </c>
       <c r="B123" t="s">
-        <v>123</v>
+        <v>142</v>
       </c>
       <c r="C123">
         <v>725</v>
@@ -9155,7 +9373,7 @@
         <v>122</v>
       </c>
       <c r="B124" t="s">
-        <v>124</v>
+        <v>143</v>
       </c>
       <c r="C124">
         <v>755</v>
@@ -9217,7 +9435,7 @@
         <v>123</v>
       </c>
       <c r="B125" t="s">
-        <v>125</v>
+        <v>144</v>
       </c>
       <c r="C125">
         <v>860</v>
@@ -9279,7 +9497,7 @@
         <v>124</v>
       </c>
       <c r="B126" t="s">
-        <v>97</v>
+        <v>116</v>
       </c>
       <c r="C126">
         <v>637</v>
@@ -9341,7 +9559,7 @@
         <v>125</v>
       </c>
       <c r="B127" t="s">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="C127">
         <v>902</v>
@@ -9403,7 +9621,7 @@
         <v>126</v>
       </c>
       <c r="B128" t="s">
-        <v>127</v>
+        <v>146</v>
       </c>
       <c r="C128">
         <v>1170</v>
@@ -9465,7 +9683,7 @@
         <v>127</v>
       </c>
       <c r="B129" t="s">
-        <v>128</v>
+        <v>147</v>
       </c>
       <c r="C129">
         <v>721</v>
@@ -9527,7 +9745,7 @@
         <v>128</v>
       </c>
       <c r="B130" t="s">
-        <v>129</v>
+        <v>148</v>
       </c>
       <c r="C130">
         <v>504</v>
@@ -9589,7 +9807,7 @@
         <v>129</v>
       </c>
       <c r="B131" t="s">
-        <v>130</v>
+        <v>149</v>
       </c>
       <c r="C131">
         <v>1001</v>
@@ -9651,7 +9869,7 @@
         <v>130</v>
       </c>
       <c r="B132" t="s">
-        <v>131</v>
+        <v>150</v>
       </c>
       <c r="C132">
         <v>1156</v>
@@ -9713,7 +9931,7 @@
         <v>131</v>
       </c>
       <c r="B133" t="s">
-        <v>132</v>
+        <v>151</v>
       </c>
       <c r="C133">
         <v>1154</v>
@@ -9775,7 +9993,7 @@
         <v>132</v>
       </c>
       <c r="B134" t="s">
-        <v>133</v>
+        <v>152</v>
       </c>
       <c r="C134">
         <v>1093</v>
@@ -9837,7 +10055,7 @@
         <v>133</v>
       </c>
       <c r="B135" t="s">
-        <v>134</v>
+        <v>153</v>
       </c>
       <c r="C135">
         <v>762</v>
@@ -9899,7 +10117,7 @@
         <v>134</v>
       </c>
       <c r="B136" t="s">
-        <v>135</v>
+        <v>154</v>
       </c>
       <c r="C136">
         <v>362</v>
@@ -9961,7 +10179,7 @@
         <v>135</v>
       </c>
       <c r="B137" t="s">
-        <v>136</v>
+        <v>155</v>
       </c>
       <c r="C137">
         <v>632</v>
@@ -10023,7 +10241,7 @@
         <v>136</v>
       </c>
       <c r="B138" t="s">
-        <v>137</v>
+        <v>156</v>
       </c>
       <c r="C138">
         <v>464</v>
@@ -10085,7 +10303,7 @@
         <v>137</v>
       </c>
       <c r="B139" t="s">
-        <v>138</v>
+        <v>157</v>
       </c>
       <c r="C139">
         <v>781</v>
@@ -10147,7 +10365,7 @@
         <v>138</v>
       </c>
       <c r="B140" t="s">
-        <v>139</v>
+        <v>158</v>
       </c>
       <c r="C140">
         <v>427</v>
@@ -10209,7 +10427,7 @@
         <v>139</v>
       </c>
       <c r="B141" t="s">
-        <v>140</v>
+        <v>159</v>
       </c>
       <c r="C141">
         <v>667</v>
@@ -10271,7 +10489,7 @@
         <v>140</v>
       </c>
       <c r="B142" t="s">
-        <v>141</v>
+        <v>160</v>
       </c>
       <c r="C142">
         <v>854</v>
@@ -10333,7 +10551,7 @@
         <v>141</v>
       </c>
       <c r="B143" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="C143">
         <v>760</v>
@@ -10395,7 +10613,7 @@
         <v>142</v>
       </c>
       <c r="B144" t="s">
-        <v>143</v>
+        <v>162</v>
       </c>
       <c r="C144">
         <v>730</v>
@@ -10457,7 +10675,7 @@
         <v>143</v>
       </c>
       <c r="B145" t="s">
-        <v>144</v>
+        <v>163</v>
       </c>
       <c r="C145">
         <v>1131</v>
@@ -10519,7 +10737,7 @@
         <v>144</v>
       </c>
       <c r="B146" t="s">
-        <v>145</v>
+        <v>164</v>
       </c>
       <c r="C146">
         <v>1035</v>
@@ -10581,7 +10799,7 @@
         <v>145</v>
       </c>
       <c r="B147" t="s">
-        <v>146</v>
+        <v>165</v>
       </c>
       <c r="C147">
         <v>721</v>
@@ -10643,7 +10861,7 @@
         <v>146</v>
       </c>
       <c r="B148" t="s">
-        <v>147</v>
+        <v>166</v>
       </c>
       <c r="C148">
         <v>1034</v>
@@ -10705,7 +10923,7 @@
         <v>147</v>
       </c>
       <c r="B149" t="s">
-        <v>148</v>
+        <v>167</v>
       </c>
       <c r="C149">
         <v>781</v>
@@ -10767,7 +10985,7 @@
         <v>148</v>
       </c>
       <c r="B150" t="s">
-        <v>149</v>
+        <v>168</v>
       </c>
       <c r="C150">
         <v>721</v>
@@ -10829,7 +11047,7 @@
         <v>149</v>
       </c>
       <c r="B151" t="s">
-        <v>150</v>
+        <v>169</v>
       </c>
       <c r="C151">
         <v>856</v>
@@ -10891,7 +11109,7 @@
         <v>150</v>
       </c>
       <c r="B152" t="s">
-        <v>151</v>
+        <v>170</v>
       </c>
       <c r="C152">
         <v>553</v>
@@ -10953,7 +11171,7 @@
         <v>151</v>
       </c>
       <c r="B153" t="s">
-        <v>152</v>
+        <v>171</v>
       </c>
       <c r="C153">
         <v>690</v>
@@ -11015,7 +11233,7 @@
         <v>152</v>
       </c>
       <c r="B154" t="s">
-        <v>153</v>
+        <v>172</v>
       </c>
       <c r="C154">
         <v>789</v>
@@ -11077,7 +11295,7 @@
         <v>153</v>
       </c>
       <c r="B155" t="s">
-        <v>154</v>
+        <v>173</v>
       </c>
       <c r="C155">
         <v>848</v>
@@ -11139,7 +11357,7 @@
         <v>154</v>
       </c>
       <c r="B156" t="s">
-        <v>155</v>
+        <v>174</v>
       </c>
       <c r="C156">
         <v>750</v>
@@ -11201,7 +11419,7 @@
         <v>155</v>
       </c>
       <c r="B157" t="s">
-        <v>156</v>
+        <v>175</v>
       </c>
       <c r="C157">
         <v>723</v>
@@ -11263,7 +11481,7 @@
         <v>156</v>
       </c>
       <c r="B158" t="s">
-        <v>157</v>
+        <v>176</v>
       </c>
       <c r="C158">
         <v>1024</v>
@@ -11325,7 +11543,7 @@
         <v>157</v>
       </c>
       <c r="B159" t="s">
-        <v>158</v>
+        <v>177</v>
       </c>
       <c r="C159">
         <v>992</v>
@@ -11387,7 +11605,7 @@
         <v>158</v>
       </c>
       <c r="B160" t="s">
-        <v>159</v>
+        <v>178</v>
       </c>
       <c r="C160">
         <v>1011</v>
@@ -11449,7 +11667,7 @@
         <v>159</v>
       </c>
       <c r="B161" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="C161">
         <v>1067</v>
@@ -11511,7 +11729,7 @@
         <v>160</v>
       </c>
       <c r="B162" t="s">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="C162">
         <v>1117</v>
@@ -11573,7 +11791,7 @@
         <v>161</v>
       </c>
       <c r="B163" t="s">
-        <v>162</v>
+        <v>181</v>
       </c>
       <c r="C163">
         <v>1134</v>
@@ -11635,7 +11853,7 @@
         <v>162</v>
       </c>
       <c r="B164" t="s">
-        <v>163</v>
+        <v>182</v>
       </c>
       <c r="C164">
         <v>1088</v>
@@ -11697,7 +11915,7 @@
         <v>163</v>
       </c>
       <c r="B165" t="s">
-        <v>164</v>
+        <v>183</v>
       </c>
       <c r="C165">
         <v>925</v>
@@ -11759,7 +11977,7 @@
         <v>164</v>
       </c>
       <c r="B166" t="s">
-        <v>165</v>
+        <v>184</v>
       </c>
       <c r="C166">
         <v>867</v>
@@ -11821,7 +12039,7 @@
         <v>165</v>
       </c>
       <c r="B167" t="s">
-        <v>166</v>
+        <v>185</v>
       </c>
       <c r="C167">
         <v>680</v>
@@ -11883,7 +12101,7 @@
         <v>166</v>
       </c>
       <c r="B168" t="s">
-        <v>167</v>
+        <v>186</v>
       </c>
       <c r="C168">
         <v>651</v>
@@ -11945,7 +12163,7 @@
         <v>167</v>
       </c>
       <c r="B169" t="s">
-        <v>168</v>
+        <v>187</v>
       </c>
       <c r="C169">
         <v>840</v>
@@ -12007,7 +12225,7 @@
         <v>168</v>
       </c>
       <c r="B170" t="s">
-        <v>169</v>
+        <v>188</v>
       </c>
       <c r="C170">
         <v>415</v>
@@ -12069,7 +12287,7 @@
         <v>169</v>
       </c>
       <c r="B171" t="s">
-        <v>170</v>
+        <v>189</v>
       </c>
       <c r="C171">
         <v>1094</v>
@@ -12131,7 +12349,7 @@
         <v>170</v>
       </c>
       <c r="B172" t="s">
-        <v>171</v>
+        <v>190</v>
       </c>
       <c r="C172">
         <v>722</v>
@@ -12193,7 +12411,7 @@
         <v>171</v>
       </c>
       <c r="B173" t="s">
-        <v>172</v>
+        <v>191</v>
       </c>
       <c r="C173">
         <v>856</v>
@@ -12255,7 +12473,7 @@
         <v>172</v>
       </c>
       <c r="B174" t="s">
-        <v>173</v>
+        <v>192</v>
       </c>
       <c r="C174">
         <v>738</v>
@@ -12317,7 +12535,7 @@
         <v>173</v>
       </c>
       <c r="B175" t="s">
-        <v>174</v>
+        <v>193</v>
       </c>
       <c r="C175">
         <v>749</v>
@@ -12379,7 +12597,7 @@
         <v>174</v>
       </c>
       <c r="B176" t="s">
-        <v>175</v>
+        <v>194</v>
       </c>
       <c r="C176">
         <v>965</v>
@@ -12441,7 +12659,7 @@
         <v>175</v>
       </c>
       <c r="B177" t="s">
-        <v>176</v>
+        <v>195</v>
       </c>
       <c r="C177">
         <v>943</v>
@@ -12503,7 +12721,7 @@
         <v>176</v>
       </c>
       <c r="B178" t="s">
-        <v>177</v>
+        <v>196</v>
       </c>
       <c r="C178">
         <v>1003</v>
@@ -12565,7 +12783,7 @@
         <v>177</v>
       </c>
       <c r="B179" t="s">
-        <v>178</v>
+        <v>197</v>
       </c>
       <c r="C179">
         <v>1117</v>
@@ -12627,7 +12845,7 @@
         <v>178</v>
       </c>
       <c r="B180" t="s">
-        <v>179</v>
+        <v>198</v>
       </c>
       <c r="C180">
         <v>1139</v>
@@ -12689,7 +12907,7 @@
         <v>179</v>
       </c>
       <c r="B181" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="C181">
         <v>799</v>
@@ -12751,7 +12969,7 @@
         <v>180</v>
       </c>
       <c r="B182" t="s">
-        <v>181</v>
+        <v>200</v>
       </c>
       <c r="C182">
         <v>740</v>
@@ -12813,7 +13031,7 @@
         <v>181</v>
       </c>
       <c r="B183" t="s">
-        <v>182</v>
+        <v>201</v>
       </c>
       <c r="C183">
         <v>784</v>
@@ -12875,7 +13093,7 @@
         <v>182</v>
       </c>
       <c r="B184" t="s">
-        <v>183</v>
+        <v>202</v>
       </c>
       <c r="C184">
         <v>688</v>
@@ -12937,7 +13155,7 @@
         <v>183</v>
       </c>
       <c r="B185" t="s">
-        <v>184</v>
+        <v>203</v>
       </c>
       <c r="C185">
         <v>485</v>
@@ -12999,7 +13217,7 @@
         <v>184</v>
       </c>
       <c r="B186" t="s">
-        <v>185</v>
+        <v>204</v>
       </c>
       <c r="C186">
         <v>1120</v>
@@ -13061,7 +13279,7 @@
         <v>185</v>
       </c>
       <c r="B187" t="s">
-        <v>186</v>
+        <v>205</v>
       </c>
       <c r="C187">
         <v>613</v>
@@ -13123,7 +13341,7 @@
         <v>186</v>
       </c>
       <c r="B188" t="s">
-        <v>187</v>
+        <v>206</v>
       </c>
       <c r="C188">
         <v>1106</v>
@@ -13185,7 +13403,7 @@
         <v>187</v>
       </c>
       <c r="B189" t="s">
-        <v>188</v>
+        <v>207</v>
       </c>
       <c r="C189">
         <v>1177</v>
@@ -13247,7 +13465,7 @@
         <v>188</v>
       </c>
       <c r="B190" t="s">
-        <v>189</v>
+        <v>208</v>
       </c>
       <c r="C190">
         <v>1023</v>
@@ -13309,7 +13527,7 @@
         <v>189</v>
       </c>
       <c r="B191" t="s">
-        <v>190</v>
+        <v>209</v>
       </c>
       <c r="C191">
         <v>928</v>
@@ -13371,7 +13589,7 @@
         <v>190</v>
       </c>
       <c r="B192" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="C192">
         <v>912</v>
@@ -13433,7 +13651,7 @@
         <v>191</v>
       </c>
       <c r="B193" t="s">
-        <v>191</v>
+        <v>210</v>
       </c>
       <c r="C193">
         <v>623</v>
@@ -13495,7 +13713,7 @@
         <v>192</v>
       </c>
       <c r="B194" t="s">
-        <v>192</v>
+        <v>211</v>
       </c>
       <c r="C194">
         <v>1043</v>
@@ -13557,7 +13775,7 @@
         <v>193</v>
       </c>
       <c r="B195" t="s">
-        <v>193</v>
+        <v>212</v>
       </c>
       <c r="C195">
         <v>635</v>
@@ -13619,7 +13837,7 @@
         <v>194</v>
       </c>
       <c r="B196" t="s">
-        <v>194</v>
+        <v>213</v>
       </c>
       <c r="C196">
         <v>572</v>
@@ -13681,7 +13899,7 @@
         <v>195</v>
       </c>
       <c r="B197" t="s">
-        <v>195</v>
+        <v>214</v>
       </c>
       <c r="C197">
         <v>949</v>
@@ -13743,7 +13961,7 @@
         <v>196</v>
       </c>
       <c r="B198" t="s">
-        <v>196</v>
+        <v>215</v>
       </c>
       <c r="C198">
         <v>748</v>
@@ -13805,7 +14023,7 @@
         <v>197</v>
       </c>
       <c r="B199" t="s">
-        <v>197</v>
+        <v>216</v>
       </c>
       <c r="C199">
         <v>801</v>
@@ -13867,7 +14085,7 @@
         <v>198</v>
       </c>
       <c r="B200" t="s">
-        <v>124</v>
+        <v>143</v>
       </c>
       <c r="C200">
         <v>732</v>
@@ -13929,7 +14147,7 @@
         <v>199</v>
       </c>
       <c r="B201" t="s">
-        <v>198</v>
+        <v>217</v>
       </c>
       <c r="C201">
         <v>981</v>
@@ -13991,7 +14209,7 @@
         <v>200</v>
       </c>
       <c r="B202" t="s">
-        <v>199</v>
+        <v>218</v>
       </c>
       <c r="C202">
         <v>968</v>
@@ -14053,7 +14271,7 @@
         <v>201</v>
       </c>
       <c r="B203" t="s">
-        <v>200</v>
+        <v>219</v>
       </c>
       <c r="C203">
         <v>635</v>
@@ -14115,7 +14333,7 @@
         <v>202</v>
       </c>
       <c r="B204" t="s">
-        <v>201</v>
+        <v>220</v>
       </c>
       <c r="C204">
         <v>832</v>
@@ -14177,7 +14395,7 @@
         <v>203</v>
       </c>
       <c r="B205" t="s">
-        <v>202</v>
+        <v>221</v>
       </c>
       <c r="C205">
         <v>723</v>
@@ -14239,7 +14457,7 @@
         <v>204</v>
       </c>
       <c r="B206" t="s">
-        <v>203</v>
+        <v>222</v>
       </c>
       <c r="C206">
         <v>1146</v>
@@ -14301,7 +14519,7 @@
         <v>205</v>
       </c>
       <c r="B207" t="s">
-        <v>204</v>
+        <v>223</v>
       </c>
       <c r="C207">
         <v>539</v>
@@ -14363,7 +14581,7 @@
         <v>206</v>
       </c>
       <c r="B208" t="s">
-        <v>205</v>
+        <v>224</v>
       </c>
       <c r="C208">
         <v>750</v>
@@ -14425,7 +14643,7 @@
         <v>207</v>
       </c>
       <c r="B209" t="s">
-        <v>206</v>
+        <v>225</v>
       </c>
       <c r="C209">
         <v>607</v>
@@ -14487,7 +14705,7 @@
         <v>208</v>
       </c>
       <c r="B210" t="s">
-        <v>207</v>
+        <v>226</v>
       </c>
       <c r="C210">
         <v>825</v>
@@ -14549,7 +14767,7 @@
         <v>209</v>
       </c>
       <c r="B211" t="s">
-        <v>208</v>
+        <v>227</v>
       </c>
       <c r="C211">
         <v>778</v>
@@ -14611,7 +14829,7 @@
         <v>210</v>
       </c>
       <c r="B212" t="s">
-        <v>209</v>
+        <v>228</v>
       </c>
       <c r="C212">
         <v>802</v>
@@ -14673,7 +14891,7 @@
         <v>211</v>
       </c>
       <c r="B213" t="s">
-        <v>210</v>
+        <v>229</v>
       </c>
       <c r="C213">
         <v>446</v>
@@ -14735,7 +14953,7 @@
         <v>212</v>
       </c>
       <c r="B214" t="s">
-        <v>211</v>
+        <v>230</v>
       </c>
       <c r="C214">
         <v>751</v>
@@ -14797,7 +15015,7 @@
         <v>213</v>
       </c>
       <c r="B215" t="s">
-        <v>212</v>
+        <v>231</v>
       </c>
       <c r="C215">
         <v>881</v>
@@ -14859,7 +15077,7 @@
         <v>214</v>
       </c>
       <c r="B216" t="s">
-        <v>213</v>
+        <v>232</v>
       </c>
       <c r="C216">
         <v>497</v>
@@ -14921,7 +15139,7 @@
         <v>215</v>
       </c>
       <c r="B217" t="s">
-        <v>214</v>
+        <v>233</v>
       </c>
       <c r="C217">
         <v>1196</v>
@@ -14983,7 +15201,7 @@
         <v>216</v>
       </c>
       <c r="B218" t="s">
-        <v>215</v>
+        <v>234</v>
       </c>
       <c r="C218">
         <v>671</v>
@@ -15045,7 +15263,7 @@
         <v>217</v>
       </c>
       <c r="B219" t="s">
-        <v>216</v>
+        <v>235</v>
       </c>
       <c r="C219">
         <v>532</v>
@@ -15107,7 +15325,7 @@
         <v>218</v>
       </c>
       <c r="B220" t="s">
-        <v>217</v>
+        <v>236</v>
       </c>
       <c r="C220">
         <v>465</v>
@@ -15169,7 +15387,7 @@
         <v>219</v>
       </c>
       <c r="B221" t="s">
-        <v>218</v>
+        <v>237</v>
       </c>
       <c r="C221">
         <v>902</v>
@@ -15231,7 +15449,7 @@
         <v>220</v>
       </c>
       <c r="B222" t="s">
-        <v>219</v>
+        <v>238</v>
       </c>
       <c r="C222">
         <v>643</v>
@@ -15293,7 +15511,7 @@
         <v>221</v>
       </c>
       <c r="B223" t="s">
-        <v>220</v>
+        <v>239</v>
       </c>
       <c r="C223">
         <v>756</v>
@@ -15355,7 +15573,7 @@
         <v>222</v>
       </c>
       <c r="B224" t="s">
-        <v>221</v>
+        <v>240</v>
       </c>
       <c r="C224">
         <v>659</v>
@@ -15417,7 +15635,7 @@
         <v>223</v>
       </c>
       <c r="B225" t="s">
-        <v>222</v>
+        <v>241</v>
       </c>
       <c r="C225">
         <v>704</v>
@@ -15479,7 +15697,7 @@
         <v>224</v>
       </c>
       <c r="B226" t="s">
-        <v>223</v>
+        <v>242</v>
       </c>
       <c r="C226">
         <v>433</v>
@@ -15541,7 +15759,7 @@
         <v>225</v>
       </c>
       <c r="B227" t="s">
-        <v>224</v>
+        <v>243</v>
       </c>
       <c r="C227">
         <v>743</v>
@@ -15603,7 +15821,7 @@
         <v>226</v>
       </c>
       <c r="B228" t="s">
-        <v>225</v>
+        <v>244</v>
       </c>
       <c r="C228">
         <v>755</v>
@@ -15665,7 +15883,7 @@
         <v>227</v>
       </c>
       <c r="B229" t="s">
-        <v>226</v>
+        <v>245</v>
       </c>
       <c r="C229">
         <v>694</v>
@@ -15727,7 +15945,7 @@
         <v>228</v>
       </c>
       <c r="B230" t="s">
-        <v>227</v>
+        <v>246</v>
       </c>
       <c r="C230">
         <v>754</v>
@@ -15789,7 +16007,7 @@
         <v>229</v>
       </c>
       <c r="B231" t="s">
-        <v>228</v>
+        <v>247</v>
       </c>
       <c r="C231">
         <v>822</v>
@@ -15851,7 +16069,7 @@
         <v>230</v>
       </c>
       <c r="B232" t="s">
-        <v>229</v>
+        <v>248</v>
       </c>
       <c r="C232">
         <v>932</v>
@@ -15913,7 +16131,7 @@
         <v>231</v>
       </c>
       <c r="B233" t="s">
-        <v>230</v>
+        <v>249</v>
       </c>
       <c r="C233">
         <v>1074</v>
@@ -15975,7 +16193,7 @@
         <v>232</v>
       </c>
       <c r="B234" t="s">
-        <v>231</v>
+        <v>250</v>
       </c>
       <c r="C234">
         <v>529</v>
@@ -16037,7 +16255,7 @@
         <v>233</v>
       </c>
       <c r="B235" t="s">
-        <v>232</v>
+        <v>251</v>
       </c>
       <c r="C235">
         <v>810</v>
@@ -16099,7 +16317,7 @@
         <v>234</v>
       </c>
       <c r="B236" t="s">
-        <v>233</v>
+        <v>252</v>
       </c>
       <c r="C236">
         <v>802</v>
@@ -16161,7 +16379,7 @@
         <v>235</v>
       </c>
       <c r="B237" t="s">
-        <v>234</v>
+        <v>253</v>
       </c>
       <c r="C237">
         <v>794</v>
@@ -16223,7 +16441,7 @@
         <v>236</v>
       </c>
       <c r="B238" t="s">
-        <v>235</v>
+        <v>254</v>
       </c>
       <c r="C238">
         <v>1158</v>
@@ -16285,7 +16503,7 @@
         <v>237</v>
       </c>
       <c r="B239" t="s">
-        <v>236</v>
+        <v>255</v>
       </c>
       <c r="C239">
         <v>1066</v>
@@ -16347,7 +16565,7 @@
         <v>238</v>
       </c>
       <c r="B240" t="s">
-        <v>237</v>
+        <v>256</v>
       </c>
       <c r="C240">
         <v>1182</v>
@@ -16409,7 +16627,7 @@
         <v>239</v>
       </c>
       <c r="B241" t="s">
-        <v>238</v>
+        <v>257</v>
       </c>
       <c r="C241">
         <v>450</v>
@@ -16471,7 +16689,7 @@
         <v>240</v>
       </c>
       <c r="B242" t="s">
-        <v>239</v>
+        <v>258</v>
       </c>
       <c r="C242">
         <v>942</v>
@@ -16533,7 +16751,7 @@
         <v>241</v>
       </c>
       <c r="B243" t="s">
-        <v>240</v>
+        <v>259</v>
       </c>
       <c r="C243">
         <v>674</v>
@@ -16595,7 +16813,7 @@
         <v>242</v>
       </c>
       <c r="B244" t="s">
-        <v>241</v>
+        <v>260</v>
       </c>
       <c r="C244">
         <v>649</v>
@@ -16657,7 +16875,7 @@
         <v>243</v>
       </c>
       <c r="B245" t="s">
-        <v>242</v>
+        <v>261</v>
       </c>
       <c r="C245">
         <v>982</v>
@@ -16719,7 +16937,7 @@
         <v>244</v>
       </c>
       <c r="B246" t="s">
-        <v>243</v>
+        <v>262</v>
       </c>
       <c r="C246">
         <v>875</v>
@@ -16781,7 +16999,7 @@
         <v>245</v>
       </c>
       <c r="B247" t="s">
-        <v>244</v>
+        <v>263</v>
       </c>
       <c r="C247">
         <v>1186</v>
@@ -16843,7 +17061,7 @@
         <v>246</v>
       </c>
       <c r="B248" t="s">
-        <v>245</v>
+        <v>264</v>
       </c>
       <c r="C248">
         <v>641</v>
@@ -16905,7 +17123,7 @@
         <v>247</v>
       </c>
       <c r="B249" t="s">
-        <v>246</v>
+        <v>265</v>
       </c>
       <c r="C249">
         <v>716</v>
@@ -16967,7 +17185,7 @@
         <v>248</v>
       </c>
       <c r="B250" t="s">
-        <v>247</v>
+        <v>266</v>
       </c>
       <c r="C250">
         <v>695</v>
@@ -17029,7 +17247,7 @@
         <v>249</v>
       </c>
       <c r="B251" t="s">
-        <v>248</v>
+        <v>267</v>
       </c>
       <c r="C251">
         <v>705</v>
@@ -17091,7 +17309,7 @@
         <v>250</v>
       </c>
       <c r="B252" t="s">
-        <v>249</v>
+        <v>268</v>
       </c>
       <c r="C252">
         <v>683</v>
@@ -17153,7 +17371,7 @@
         <v>251</v>
       </c>
       <c r="B253" t="s">
-        <v>250</v>
+        <v>269</v>
       </c>
       <c r="C253">
         <v>1107</v>
@@ -17215,7 +17433,7 @@
         <v>252</v>
       </c>
       <c r="B254" t="s">
-        <v>251</v>
+        <v>270</v>
       </c>
       <c r="C254">
         <v>1129</v>
@@ -17277,7 +17495,7 @@
         <v>253</v>
       </c>
       <c r="B255" t="s">
-        <v>252</v>
+        <v>271</v>
       </c>
       <c r="C255">
         <v>1137</v>
@@ -17339,7 +17557,7 @@
         <v>254</v>
       </c>
       <c r="B256" t="s">
-        <v>253</v>
+        <v>272</v>
       </c>
       <c r="C256">
         <v>384</v>
@@ -17401,7 +17619,7 @@
         <v>255</v>
       </c>
       <c r="B257" t="s">
-        <v>254</v>
+        <v>273</v>
       </c>
       <c r="C257">
         <v>744</v>
@@ -17463,7 +17681,7 @@
         <v>256</v>
       </c>
       <c r="B258" t="s">
-        <v>255</v>
+        <v>274</v>
       </c>
       <c r="C258">
         <v>511</v>
@@ -17525,7 +17743,7 @@
         <v>257</v>
       </c>
       <c r="B259" t="s">
-        <v>256</v>
+        <v>275</v>
       </c>
       <c r="C259">
         <v>636</v>
@@ -17587,7 +17805,7 @@
         <v>258</v>
       </c>
       <c r="B260" t="s">
-        <v>257</v>
+        <v>276</v>
       </c>
       <c r="C260">
         <v>1024</v>
@@ -17649,7 +17867,7 @@
         <v>259</v>
       </c>
       <c r="B261" t="s">
-        <v>258</v>
+        <v>277</v>
       </c>
       <c r="C261">
         <v>355</v>
@@ -17711,7 +17929,7 @@
         <v>260</v>
       </c>
       <c r="B262" t="s">
-        <v>259</v>
+        <v>278</v>
       </c>
       <c r="C262">
         <v>854</v>
@@ -17773,7 +17991,7 @@
         <v>261</v>
       </c>
       <c r="B263" t="s">
-        <v>259</v>
+        <v>278</v>
       </c>
       <c r="C263">
         <v>1095</v>
@@ -17835,7 +18053,7 @@
         <v>262</v>
       </c>
       <c r="B264" t="s">
-        <v>260</v>
+        <v>279</v>
       </c>
       <c r="C264">
         <v>1134</v>
@@ -17897,7 +18115,7 @@
         <v>263</v>
       </c>
       <c r="B265" t="s">
-        <v>261</v>
+        <v>280</v>
       </c>
       <c r="C265">
         <v>627</v>
@@ -17959,7 +18177,7 @@
         <v>264</v>
       </c>
       <c r="B266" t="s">
-        <v>262</v>
+        <v>281</v>
       </c>
       <c r="C266">
         <v>586</v>
@@ -18021,7 +18239,7 @@
         <v>265</v>
       </c>
       <c r="B267" t="s">
-        <v>263</v>
+        <v>282</v>
       </c>
       <c r="C267">
         <v>696</v>
@@ -18083,7 +18301,7 @@
         <v>266</v>
       </c>
       <c r="B268" t="s">
-        <v>264</v>
+        <v>283</v>
       </c>
       <c r="C268">
         <v>1035</v>
@@ -18145,7 +18363,7 @@
         <v>267</v>
       </c>
       <c r="B269" t="s">
-        <v>265</v>
+        <v>284</v>
       </c>
       <c r="C269">
         <v>851</v>
@@ -18207,7 +18425,7 @@
         <v>268</v>
       </c>
       <c r="B270" t="s">
-        <v>266</v>
+        <v>285</v>
       </c>
       <c r="C270">
         <v>841</v>
@@ -18269,7 +18487,7 @@
         <v>269</v>
       </c>
       <c r="B271" t="s">
-        <v>267</v>
+        <v>286</v>
       </c>
       <c r="C271">
         <v>868</v>
@@ -18331,7 +18549,7 @@
         <v>270</v>
       </c>
       <c r="B272" t="s">
-        <v>268</v>
+        <v>287</v>
       </c>
       <c r="C272">
         <v>370</v>
@@ -18393,7 +18611,7 @@
         <v>271</v>
       </c>
       <c r="B273" t="s">
-        <v>269</v>
+        <v>288</v>
       </c>
       <c r="C273">
         <v>875</v>
@@ -18455,7 +18673,7 @@
         <v>272</v>
       </c>
       <c r="B274" t="s">
-        <v>270</v>
+        <v>289</v>
       </c>
       <c r="C274">
         <v>932</v>
@@ -18517,7 +18735,7 @@
         <v>273</v>
       </c>
       <c r="B275" t="s">
-        <v>271</v>
+        <v>290</v>
       </c>
       <c r="C275">
         <v>1023</v>
@@ -18579,7 +18797,7 @@
         <v>274</v>
       </c>
       <c r="B276" t="s">
-        <v>272</v>
+        <v>291</v>
       </c>
       <c r="C276">
         <v>810</v>
@@ -18641,7 +18859,7 @@
         <v>275</v>
       </c>
       <c r="B277" t="s">
-        <v>273</v>
+        <v>292</v>
       </c>
       <c r="C277">
         <v>784</v>
@@ -18703,7 +18921,7 @@
         <v>276</v>
       </c>
       <c r="B278" t="s">
-        <v>274</v>
+        <v>293</v>
       </c>
       <c r="C278">
         <v>933</v>
@@ -18765,7 +18983,7 @@
         <v>277</v>
       </c>
       <c r="B279" t="s">
-        <v>275</v>
+        <v>294</v>
       </c>
       <c r="C279">
         <v>910</v>
@@ -18827,7 +19045,7 @@
         <v>278</v>
       </c>
       <c r="B280" t="s">
-        <v>276</v>
+        <v>295</v>
       </c>
       <c r="C280">
         <v>757</v>
@@ -18889,7 +19107,7 @@
         <v>279</v>
       </c>
       <c r="B281" t="s">
-        <v>277</v>
+        <v>296</v>
       </c>
       <c r="C281">
         <v>672</v>
@@ -18951,7 +19169,7 @@
         <v>280</v>
       </c>
       <c r="B282" t="s">
-        <v>278</v>
+        <v>297</v>
       </c>
       <c r="C282">
         <v>633</v>
@@ -19013,7 +19231,7 @@
         <v>281</v>
       </c>
       <c r="B283" t="s">
-        <v>279</v>
+        <v>298</v>
       </c>
       <c r="C283">
         <v>826</v>
@@ -19075,7 +19293,7 @@
         <v>282</v>
       </c>
       <c r="B284" t="s">
-        <v>280</v>
+        <v>299</v>
       </c>
       <c r="C284">
         <v>409</v>
@@ -19137,7 +19355,7 @@
         <v>283</v>
       </c>
       <c r="B285" t="s">
-        <v>281</v>
+        <v>300</v>
       </c>
       <c r="C285">
         <v>742</v>
@@ -19199,7 +19417,7 @@
         <v>284</v>
       </c>
       <c r="B286" t="s">
-        <v>282</v>
+        <v>301</v>
       </c>
       <c r="C286">
         <v>638</v>
@@ -19261,7 +19479,7 @@
         <v>285</v>
       </c>
       <c r="B287" t="s">
-        <v>283</v>
+        <v>302</v>
       </c>
       <c r="C287">
         <v>464</v>
@@ -19323,7 +19541,7 @@
         <v>286</v>
       </c>
       <c r="B288" t="s">
-        <v>284</v>
+        <v>303</v>
       </c>
       <c r="C288">
         <v>553</v>
@@ -19385,7 +19603,7 @@
         <v>287</v>
       </c>
       <c r="B289" t="s">
-        <v>285</v>
+        <v>304</v>
       </c>
       <c r="C289">
         <v>796</v>
@@ -19447,7 +19665,7 @@
         <v>288</v>
       </c>
       <c r="B290" t="s">
-        <v>286</v>
+        <v>305</v>
       </c>
       <c r="C290">
         <v>831</v>
@@ -19509,7 +19727,7 @@
         <v>289</v>
       </c>
       <c r="B291" t="s">
-        <v>287</v>
+        <v>306</v>
       </c>
       <c r="C291">
         <v>1165</v>
@@ -19571,7 +19789,7 @@
         <v>290</v>
       </c>
       <c r="B292" t="s">
-        <v>288</v>
+        <v>307</v>
       </c>
       <c r="C292">
         <v>885</v>
@@ -19633,7 +19851,7 @@
         <v>291</v>
       </c>
       <c r="B293" t="s">
-        <v>289</v>
+        <v>308</v>
       </c>
       <c r="C293">
         <v>949</v>
@@ -19695,7 +19913,7 @@
         <v>292</v>
       </c>
       <c r="B294" t="s">
-        <v>290</v>
+        <v>309</v>
       </c>
       <c r="C294">
         <v>941</v>
@@ -19757,7 +19975,7 @@
         <v>293</v>
       </c>
       <c r="B295" t="s">
-        <v>291</v>
+        <v>310</v>
       </c>
       <c r="C295">
         <v>848</v>
@@ -19819,7 +20037,7 @@
         <v>294</v>
       </c>
       <c r="B296" t="s">
-        <v>292</v>
+        <v>311</v>
       </c>
       <c r="C296">
         <v>948</v>
@@ -19881,7 +20099,7 @@
         <v>295</v>
       </c>
       <c r="B297" t="s">
-        <v>293</v>
+        <v>312</v>
       </c>
       <c r="C297">
         <v>559</v>
@@ -19943,7 +20161,7 @@
         <v>296</v>
       </c>
       <c r="B298" t="s">
-        <v>294</v>
+        <v>313</v>
       </c>
       <c r="C298">
         <v>648</v>
@@ -20005,7 +20223,7 @@
         <v>297</v>
       </c>
       <c r="B299" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
       <c r="C299">
         <v>711</v>
@@ -20067,7 +20285,7 @@
         <v>298</v>
       </c>
       <c r="B300" t="s">
-        <v>296</v>
+        <v>315</v>
       </c>
       <c r="C300">
         <v>664</v>
@@ -20129,7 +20347,7 @@
         <v>299</v>
       </c>
       <c r="B301" t="s">
-        <v>297</v>
+        <v>316</v>
       </c>
       <c r="C301">
         <v>583</v>
@@ -20191,7 +20409,7 @@
         <v>300</v>
       </c>
       <c r="B302" t="s">
-        <v>298</v>
+        <v>317</v>
       </c>
       <c r="C302">
         <v>796</v>
@@ -20253,7 +20471,7 @@
         <v>301</v>
       </c>
       <c r="B303" t="s">
-        <v>299</v>
+        <v>318</v>
       </c>
       <c r="C303">
         <v>1095</v>
@@ -20315,7 +20533,7 @@
         <v>302</v>
       </c>
       <c r="B304" t="s">
-        <v>300</v>
+        <v>319</v>
       </c>
       <c r="C304">
         <v>827</v>
@@ -20377,7 +20595,7 @@
         <v>303</v>
       </c>
       <c r="B305" t="s">
-        <v>301</v>
+        <v>320</v>
       </c>
       <c r="C305">
         <v>785</v>
@@ -20439,7 +20657,7 @@
         <v>304</v>
       </c>
       <c r="B306" t="s">
-        <v>302</v>
+        <v>321</v>
       </c>
       <c r="C306">
         <v>716</v>
@@ -20501,7 +20719,7 @@
         <v>305</v>
       </c>
       <c r="B307" t="s">
-        <v>303</v>
+        <v>322</v>
       </c>
       <c r="C307">
         <v>759</v>
@@ -20563,7 +20781,7 @@
         <v>306</v>
       </c>
       <c r="B308" t="s">
-        <v>304</v>
+        <v>323</v>
       </c>
       <c r="C308">
         <v>1093</v>
@@ -20625,7 +20843,7 @@
         <v>307</v>
       </c>
       <c r="B309" t="s">
-        <v>305</v>
+        <v>324</v>
       </c>
       <c r="C309">
         <v>419</v>
@@ -20687,7 +20905,7 @@
         <v>308</v>
       </c>
       <c r="B310" t="s">
-        <v>306</v>
+        <v>325</v>
       </c>
       <c r="C310">
         <v>773</v>
@@ -20749,7 +20967,7 @@
         <v>309</v>
       </c>
       <c r="B311" t="s">
-        <v>307</v>
+        <v>326</v>
       </c>
       <c r="C311">
         <v>836</v>
@@ -20811,7 +21029,7 @@
         <v>310</v>
       </c>
       <c r="B312" t="s">
-        <v>308</v>
+        <v>327</v>
       </c>
       <c r="C312">
         <v>803</v>
@@ -20873,7 +21091,7 @@
         <v>311</v>
       </c>
       <c r="B313" t="s">
-        <v>309</v>
+        <v>328</v>
       </c>
       <c r="C313">
         <v>736</v>
@@ -20935,7 +21153,7 @@
         <v>312</v>
       </c>
       <c r="B314" t="s">
-        <v>310</v>
+        <v>329</v>
       </c>
       <c r="C314">
         <v>1041</v>
@@ -20997,7 +21215,7 @@
         <v>313</v>
       </c>
       <c r="B315" t="s">
-        <v>311</v>
+        <v>330</v>
       </c>
       <c r="C315">
         <v>1078</v>
@@ -21059,7 +21277,7 @@
         <v>314</v>
       </c>
       <c r="B316" t="s">
-        <v>312</v>
+        <v>331</v>
       </c>
       <c r="C316">
         <v>1003</v>
@@ -21121,7 +21339,7 @@
         <v>315</v>
       </c>
       <c r="B317" t="s">
-        <v>313</v>
+        <v>332</v>
       </c>
       <c r="C317">
         <v>692</v>
@@ -21183,7 +21401,7 @@
         <v>316</v>
       </c>
       <c r="B318" t="s">
-        <v>314</v>
+        <v>333</v>
       </c>
       <c r="C318">
         <v>904</v>
@@ -21245,7 +21463,7 @@
         <v>317</v>
       </c>
       <c r="B319" t="s">
-        <v>315</v>
+        <v>334</v>
       </c>
       <c r="C319">
         <v>845</v>
@@ -21307,7 +21525,7 @@
         <v>318</v>
       </c>
       <c r="B320" t="s">
-        <v>316</v>
+        <v>335</v>
       </c>
       <c r="C320">
         <v>871</v>
@@ -21369,7 +21587,7 @@
         <v>319</v>
       </c>
       <c r="B321" t="s">
-        <v>317</v>
+        <v>336</v>
       </c>
       <c r="C321">
         <v>1125</v>
@@ -21431,7 +21649,7 @@
         <v>320</v>
       </c>
       <c r="B322" t="s">
-        <v>318</v>
+        <v>337</v>
       </c>
       <c r="C322">
         <v>577</v>
@@ -21493,7 +21711,7 @@
         <v>321</v>
       </c>
       <c r="B323" t="s">
-        <v>319</v>
+        <v>338</v>
       </c>
       <c r="C323">
         <v>798</v>
@@ -21555,7 +21773,7 @@
         <v>322</v>
       </c>
       <c r="B324" t="s">
-        <v>320</v>
+        <v>339</v>
       </c>
       <c r="C324">
         <v>680</v>
@@ -21617,7 +21835,7 @@
         <v>323</v>
       </c>
       <c r="B325" t="s">
-        <v>321</v>
+        <v>340</v>
       </c>
       <c r="C325">
         <v>624</v>
@@ -21679,7 +21897,7 @@
         <v>324</v>
       </c>
       <c r="B326" t="s">
-        <v>322</v>
+        <v>341</v>
       </c>
       <c r="C326">
         <v>1056</v>
@@ -21741,7 +21959,7 @@
         <v>325</v>
       </c>
       <c r="B327" t="s">
-        <v>323</v>
+        <v>342</v>
       </c>
       <c r="C327">
         <v>721</v>
@@ -21803,7 +22021,7 @@
         <v>326</v>
       </c>
       <c r="B328" t="s">
-        <v>324</v>
+        <v>343</v>
       </c>
       <c r="C328">
         <v>872</v>
@@ -21865,7 +22083,7 @@
         <v>327</v>
       </c>
       <c r="B329" t="s">
-        <v>325</v>
+        <v>344</v>
       </c>
       <c r="C329">
         <v>1098</v>
@@ -21927,7 +22145,7 @@
         <v>328</v>
       </c>
       <c r="B330" t="s">
-        <v>326</v>
+        <v>345</v>
       </c>
       <c r="C330">
         <v>863</v>
@@ -21989,7 +22207,7 @@
         <v>329</v>
       </c>
       <c r="B331" t="s">
-        <v>327</v>
+        <v>346</v>
       </c>
       <c r="C331">
         <v>627</v>
@@ -22051,7 +22269,7 @@
         <v>330</v>
       </c>
       <c r="B332" t="s">
-        <v>328</v>
+        <v>347</v>
       </c>
       <c r="C332">
         <v>1058</v>
@@ -22113,7 +22331,7 @@
         <v>331</v>
       </c>
       <c r="B333" t="s">
-        <v>329</v>
+        <v>348</v>
       </c>
       <c r="C333">
         <v>744</v>
@@ -22175,7 +22393,7 @@
         <v>332</v>
       </c>
       <c r="B334" t="s">
-        <v>330</v>
+        <v>349</v>
       </c>
       <c r="C334">
         <v>716</v>
@@ -22237,7 +22455,7 @@
         <v>333</v>
       </c>
       <c r="B335" t="s">
-        <v>331</v>
+        <v>350</v>
       </c>
       <c r="C335">
         <v>736</v>
@@ -22299,7 +22517,7 @@
         <v>334</v>
       </c>
       <c r="B336" t="s">
-        <v>332</v>
+        <v>351</v>
       </c>
       <c r="C336">
         <v>482</v>
@@ -22361,7 +22579,7 @@
         <v>335</v>
       </c>
       <c r="B337" t="s">
-        <v>333</v>
+        <v>352</v>
       </c>
       <c r="C337">
         <v>1132</v>
@@ -22423,7 +22641,7 @@
         <v>336</v>
       </c>
       <c r="B338" t="s">
-        <v>334</v>
+        <v>353</v>
       </c>
       <c r="C338">
         <v>1101</v>
@@ -22485,7 +22703,7 @@
         <v>337</v>
       </c>
       <c r="B339" t="s">
-        <v>335</v>
+        <v>354</v>
       </c>
       <c r="C339">
         <v>1156</v>
@@ -22547,7 +22765,7 @@
         <v>338</v>
       </c>
       <c r="B340" t="s">
-        <v>336</v>
+        <v>355</v>
       </c>
       <c r="C340">
         <v>886</v>
@@ -22609,7 +22827,7 @@
         <v>339</v>
       </c>
       <c r="B341" t="s">
-        <v>337</v>
+        <v>356</v>
       </c>
       <c r="C341">
         <v>931</v>
@@ -22671,7 +22889,7 @@
         <v>340</v>
       </c>
       <c r="B342" t="s">
-        <v>338</v>
+        <v>357</v>
       </c>
       <c r="C342">
         <v>1081</v>
@@ -22733,7 +22951,7 @@
         <v>341</v>
       </c>
       <c r="B343" t="s">
-        <v>339</v>
+        <v>358</v>
       </c>
       <c r="C343">
         <v>685</v>
@@ -22795,7 +23013,7 @@
         <v>342</v>
       </c>
       <c r="B344" t="s">
-        <v>340</v>
+        <v>359</v>
       </c>
       <c r="C344">
         <v>586</v>
@@ -22857,7 +23075,7 @@
         <v>343</v>
       </c>
       <c r="B345" t="s">
-        <v>341</v>
+        <v>360</v>
       </c>
       <c r="C345">
         <v>843</v>
@@ -22919,7 +23137,7 @@
         <v>344</v>
       </c>
       <c r="B346" t="s">
-        <v>342</v>
+        <v>361</v>
       </c>
       <c r="C346">
         <v>788</v>
@@ -22981,7 +23199,7 @@
         <v>345</v>
       </c>
       <c r="B347" t="s">
-        <v>343</v>
+        <v>362</v>
       </c>
       <c r="C347">
         <v>575</v>
@@ -23043,7 +23261,7 @@
         <v>346</v>
       </c>
       <c r="B348" t="s">
-        <v>344</v>
+        <v>363</v>
       </c>
       <c r="C348">
         <v>732</v>
@@ -23105,7 +23323,7 @@
         <v>347</v>
       </c>
       <c r="B349" t="s">
-        <v>345</v>
+        <v>364</v>
       </c>
       <c r="C349">
         <v>392</v>
@@ -23167,7 +23385,7 @@
         <v>348</v>
       </c>
       <c r="B350" t="s">
-        <v>346</v>
+        <v>365</v>
       </c>
       <c r="C350">
         <v>938</v>
@@ -23229,7 +23447,7 @@
         <v>349</v>
       </c>
       <c r="B351" t="s">
-        <v>347</v>
+        <v>366</v>
       </c>
       <c r="C351">
         <v>715</v>
@@ -23291,7 +23509,7 @@
         <v>350</v>
       </c>
       <c r="B352" t="s">
-        <v>348</v>
+        <v>367</v>
       </c>
       <c r="C352">
         <v>1115</v>
@@ -23353,7 +23571,7 @@
         <v>351</v>
       </c>
       <c r="B353" t="s">
-        <v>349</v>
+        <v>368</v>
       </c>
       <c r="C353">
         <v>886</v>
@@ -23415,7 +23633,7 @@
         <v>352</v>
       </c>
       <c r="B354" t="s">
-        <v>350</v>
+        <v>369</v>
       </c>
       <c r="C354">
         <v>836</v>
@@ -23477,7 +23695,7 @@
         <v>353</v>
       </c>
       <c r="B355" t="s">
-        <v>351</v>
+        <v>370</v>
       </c>
       <c r="C355">
         <v>780</v>
@@ -23539,7 +23757,7 @@
         <v>354</v>
       </c>
       <c r="B356" t="s">
-        <v>352</v>
+        <v>371</v>
       </c>
       <c r="C356">
         <v>753</v>
@@ -23601,7 +23819,7 @@
         <v>355</v>
       </c>
       <c r="B357" t="s">
-        <v>353</v>
+        <v>372</v>
       </c>
       <c r="C357">
         <v>698</v>
@@ -23663,7 +23881,7 @@
         <v>356</v>
       </c>
       <c r="B358" t="s">
-        <v>354</v>
+        <v>373</v>
       </c>
       <c r="C358">
         <v>754</v>
@@ -23725,7 +23943,7 @@
         <v>357</v>
       </c>
       <c r="B359" t="s">
-        <v>355</v>
+        <v>374</v>
       </c>
       <c r="C359">
         <v>1068</v>
@@ -23787,7 +24005,7 @@
         <v>358</v>
       </c>
       <c r="B360" t="s">
-        <v>356</v>
+        <v>375</v>
       </c>
       <c r="C360">
         <v>977</v>
@@ -23849,7 +24067,7 @@
         <v>359</v>
       </c>
       <c r="B361" t="s">
-        <v>357</v>
+        <v>376</v>
       </c>
       <c r="C361">
         <v>1053</v>
@@ -23911,7 +24129,7 @@
         <v>360</v>
       </c>
       <c r="B362" t="s">
-        <v>358</v>
+        <v>377</v>
       </c>
       <c r="C362">
         <v>573</v>
@@ -23973,7 +24191,7 @@
         <v>361</v>
       </c>
       <c r="B363" t="s">
-        <v>359</v>
+        <v>378</v>
       </c>
       <c r="C363">
         <v>1163</v>
@@ -24035,7 +24253,7 @@
         <v>362</v>
       </c>
       <c r="B364" t="s">
-        <v>360</v>
+        <v>379</v>
       </c>
       <c r="C364">
         <v>1101</v>
@@ -24097,7 +24315,7 @@
         <v>363</v>
       </c>
       <c r="B365" t="s">
-        <v>361</v>
+        <v>380</v>
       </c>
       <c r="C365">
         <v>1142</v>
@@ -24159,7 +24377,7 @@
         <v>364</v>
       </c>
       <c r="B366" t="s">
-        <v>362</v>
+        <v>381</v>
       </c>
       <c r="C366">
         <v>733</v>
@@ -24221,7 +24439,7 @@
         <v>365</v>
       </c>
       <c r="B367" t="s">
-        <v>363</v>
+        <v>382</v>
       </c>
       <c r="C367">
         <v>776</v>
@@ -24283,7 +24501,7 @@
         <v>366</v>
       </c>
       <c r="B368" t="s">
-        <v>364</v>
+        <v>383</v>
       </c>
       <c r="C368">
         <v>730</v>
@@ -24345,7 +24563,7 @@
         <v>367</v>
       </c>
       <c r="B369" t="s">
-        <v>365</v>
+        <v>384</v>
       </c>
       <c r="C369">
         <v>706</v>
@@ -24407,7 +24625,7 @@
         <v>368</v>
       </c>
       <c r="B370" t="s">
-        <v>366</v>
+        <v>385</v>
       </c>
       <c r="C370">
         <v>902</v>
@@ -24469,7 +24687,7 @@
         <v>369</v>
       </c>
       <c r="B371" t="s">
-        <v>367</v>
+        <v>386</v>
       </c>
       <c r="C371">
         <v>663</v>
@@ -24531,7 +24749,7 @@
         <v>370</v>
       </c>
       <c r="B372" t="s">
-        <v>368</v>
+        <v>387</v>
       </c>
       <c r="C372">
         <v>699</v>
@@ -24593,7 +24811,7 @@
         <v>371</v>
       </c>
       <c r="B373" t="s">
-        <v>369</v>
+        <v>388</v>
       </c>
       <c r="C373">
         <v>602</v>
@@ -24655,7 +24873,7 @@
         <v>372</v>
       </c>
       <c r="B374" t="s">
-        <v>370</v>
+        <v>389</v>
       </c>
       <c r="C374">
         <v>729</v>
@@ -24717,7 +24935,7 @@
         <v>373</v>
       </c>
       <c r="B375" t="s">
-        <v>371</v>
+        <v>390</v>
       </c>
       <c r="C375">
         <v>569</v>
@@ -24779,7 +24997,7 @@
         <v>374</v>
       </c>
       <c r="B376" t="s">
-        <v>372</v>
+        <v>391</v>
       </c>
       <c r="C376">
         <v>686</v>
@@ -24841,7 +25059,7 @@
         <v>375</v>
       </c>
       <c r="B377" t="s">
-        <v>373</v>
+        <v>392</v>
       </c>
       <c r="C377">
         <v>662</v>
@@ -24903,7 +25121,7 @@
         <v>376</v>
       </c>
       <c r="B378" t="s">
-        <v>374</v>
+        <v>393</v>
       </c>
       <c r="C378">
         <v>649</v>
@@ -24965,7 +25183,7 @@
         <v>377</v>
       </c>
       <c r="B379" t="s">
-        <v>375</v>
+        <v>394</v>
       </c>
       <c r="C379">
         <v>692</v>
@@ -25027,7 +25245,7 @@
         <v>378</v>
       </c>
       <c r="B380" t="s">
-        <v>376</v>
+        <v>395</v>
       </c>
       <c r="C380">
         <v>1125</v>
@@ -25089,7 +25307,7 @@
         <v>379</v>
       </c>
       <c r="B381" t="s">
-        <v>377</v>
+        <v>396</v>
       </c>
       <c r="C381">
         <v>671</v>
@@ -25151,7 +25369,7 @@
         <v>380</v>
       </c>
       <c r="B382" t="s">
-        <v>378</v>
+        <v>397</v>
       </c>
       <c r="C382">
         <v>564</v>
@@ -25213,7 +25431,7 @@
         <v>381</v>
       </c>
       <c r="B383" t="s">
-        <v>379</v>
+        <v>398</v>
       </c>
       <c r="C383">
         <v>839</v>
@@ -25275,7 +25493,7 @@
         <v>382</v>
       </c>
       <c r="B384" t="s">
-        <v>376</v>
+        <v>399</v>
       </c>
       <c r="C384">
         <v>805</v>
@@ -25337,7 +25555,7 @@
         <v>383</v>
       </c>
       <c r="B385" t="s">
-        <v>380</v>
+        <v>400</v>
       </c>
       <c r="C385">
         <v>903</v>
@@ -25399,7 +25617,7 @@
         <v>384</v>
       </c>
       <c r="B386" t="s">
-        <v>381</v>
+        <v>401</v>
       </c>
       <c r="C386">
         <v>1007</v>
@@ -25461,7 +25679,7 @@
         <v>385</v>
       </c>
       <c r="B387" t="s">
-        <v>381</v>
+        <v>402</v>
       </c>
       <c r="C387">
         <v>950</v>
@@ -25523,7 +25741,7 @@
         <v>386</v>
       </c>
       <c r="B388" t="s">
-        <v>382</v>
+        <v>403</v>
       </c>
       <c r="C388">
         <v>1090</v>
@@ -25585,7 +25803,7 @@
         <v>387</v>
       </c>
       <c r="B389" t="s">
-        <v>382</v>
+        <v>404</v>
       </c>
       <c r="C389">
         <v>803</v>
@@ -25647,7 +25865,7 @@
         <v>388</v>
       </c>
       <c r="B390" t="s">
-        <v>383</v>
+        <v>405</v>
       </c>
       <c r="C390">
         <v>789</v>
@@ -25709,7 +25927,7 @@
         <v>389</v>
       </c>
       <c r="B391" t="s">
-        <v>383</v>
+        <v>406</v>
       </c>
       <c r="C391">
         <v>653</v>
@@ -25771,7 +25989,7 @@
         <v>390</v>
       </c>
       <c r="B392" t="s">
-        <v>384</v>
+        <v>407</v>
       </c>
       <c r="C392">
         <v>1093</v>
@@ -25833,7 +26051,7 @@
         <v>391</v>
       </c>
       <c r="B393" t="s">
-        <v>368</v>
+        <v>408</v>
       </c>
       <c r="C393">
         <v>479</v>
@@ -25895,7 +26113,7 @@
         <v>392</v>
       </c>
       <c r="B394" t="s">
-        <v>382</v>
+        <v>409</v>
       </c>
       <c r="C394">
         <v>466</v>
@@ -25957,7 +26175,7 @@
         <v>393</v>
       </c>
       <c r="B395" t="s">
-        <v>382</v>
+        <v>410</v>
       </c>
       <c r="C395">
         <v>853</v>
@@ -26019,7 +26237,7 @@
         <v>394</v>
       </c>
       <c r="B396" t="s">
-        <v>384</v>
+        <v>411</v>
       </c>
       <c r="C396">
         <v>793</v>
@@ -26081,7 +26299,7 @@
         <v>395</v>
       </c>
       <c r="B397" t="s">
-        <v>384</v>
+        <v>412</v>
       </c>
       <c r="C397">
         <v>724</v>
@@ -26143,7 +26361,7 @@
         <v>396</v>
       </c>
       <c r="B398" t="s">
-        <v>365</v>
+        <v>413</v>
       </c>
       <c r="C398">
         <v>912</v>
@@ -26205,7 +26423,7 @@
         <v>397</v>
       </c>
       <c r="B399" t="s">
-        <v>365</v>
+        <v>414</v>
       </c>
       <c r="C399">
         <v>901</v>
@@ -26267,7 +26485,7 @@
         <v>398</v>
       </c>
       <c r="B400" t="s">
-        <v>365</v>
+        <v>415</v>
       </c>
       <c r="C400">
         <v>766</v>
@@ -26329,7 +26547,7 @@
         <v>399</v>
       </c>
       <c r="B401" t="s">
-        <v>385</v>
+        <v>416</v>
       </c>
       <c r="C401">
         <v>477</v>
@@ -26391,7 +26609,7 @@
         <v>400</v>
       </c>
       <c r="B402" t="s">
-        <v>365</v>
+        <v>417</v>
       </c>
       <c r="C402">
         <v>1080</v>
@@ -26453,7 +26671,7 @@
         <v>401</v>
       </c>
       <c r="B403" t="s">
-        <v>365</v>
+        <v>418</v>
       </c>
       <c r="C403">
         <v>700</v>
@@ -26515,7 +26733,7 @@
         <v>402</v>
       </c>
       <c r="B404" t="s">
-        <v>365</v>
+        <v>419</v>
       </c>
       <c r="C404">
         <v>741</v>
@@ -26577,7 +26795,7 @@
         <v>403</v>
       </c>
       <c r="B405" t="s">
-        <v>365</v>
+        <v>420</v>
       </c>
       <c r="C405">
         <v>795</v>
@@ -26639,7 +26857,7 @@
         <v>404</v>
       </c>
       <c r="B406" t="s">
-        <v>386</v>
+        <v>421</v>
       </c>
       <c r="C406">
         <v>1007</v>
@@ -26701,7 +26919,7 @@
         <v>405</v>
       </c>
       <c r="B407" t="s">
-        <v>386</v>
+        <v>422</v>
       </c>
       <c r="C407">
         <v>980</v>
@@ -26763,7 +26981,7 @@
         <v>406</v>
       </c>
       <c r="B408" t="s">
-        <v>387</v>
+        <v>423</v>
       </c>
       <c r="C408">
         <v>1186</v>
@@ -26825,7 +27043,7 @@
         <v>407</v>
       </c>
       <c r="B409" t="s">
-        <v>368</v>
+        <v>424</v>
       </c>
       <c r="C409">
         <v>887</v>
@@ -26887,7 +27105,7 @@
         <v>408</v>
       </c>
       <c r="B410" t="s">
-        <v>365</v>
+        <v>425</v>
       </c>
       <c r="C410">
         <v>839</v>
@@ -26949,7 +27167,7 @@
         <v>409</v>
       </c>
       <c r="B411" t="s">
-        <v>365</v>
+        <v>426</v>
       </c>
       <c r="C411">
         <v>749</v>
@@ -27011,7 +27229,7 @@
         <v>410</v>
       </c>
       <c r="B412" t="s">
-        <v>365</v>
+        <v>427</v>
       </c>
       <c r="C412">
         <v>834</v>
@@ -27073,7 +27291,7 @@
         <v>411</v>
       </c>
       <c r="B413" t="s">
-        <v>365</v>
+        <v>428</v>
       </c>
       <c r="C413">
         <v>1057</v>
@@ -27135,7 +27353,7 @@
         <v>412</v>
       </c>
       <c r="B414" t="s">
-        <v>388</v>
+        <v>429</v>
       </c>
       <c r="C414">
         <v>1151</v>
@@ -27197,7 +27415,7 @@
         <v>413</v>
       </c>
       <c r="B415" t="s">
-        <v>389</v>
+        <v>430</v>
       </c>
       <c r="C415">
         <v>956</v>
@@ -27259,7 +27477,7 @@
         <v>414</v>
       </c>
       <c r="B416" t="s">
-        <v>384</v>
+        <v>431</v>
       </c>
       <c r="C416">
         <v>851</v>
@@ -27321,7 +27539,7 @@
         <v>415</v>
       </c>
       <c r="B417" t="s">
-        <v>384</v>
+        <v>432</v>
       </c>
       <c r="C417">
         <v>887</v>
@@ -27383,7 +27601,7 @@
         <v>416</v>
       </c>
       <c r="B418" t="s">
-        <v>390</v>
+        <v>433</v>
       </c>
       <c r="C418">
         <v>873</v>
@@ -27445,7 +27663,7 @@
         <v>417</v>
       </c>
       <c r="B419" t="s">
-        <v>390</v>
+        <v>434</v>
       </c>
       <c r="C419">
         <v>783</v>
@@ -27507,7 +27725,7 @@
         <v>418</v>
       </c>
       <c r="B420" t="s">
-        <v>365</v>
+        <v>435</v>
       </c>
       <c r="C420">
         <v>442</v>
@@ -27569,7 +27787,7 @@
         <v>419</v>
       </c>
       <c r="B421" t="s">
-        <v>391</v>
+        <v>436</v>
       </c>
       <c r="C421">
         <v>795</v>
@@ -27631,7 +27849,7 @@
         <v>420</v>
       </c>
       <c r="B422" t="s">
-        <v>392</v>
+        <v>437</v>
       </c>
       <c r="C422">
         <v>871</v>
